--- a/JsonConverter/ExcelFiles/OO_Recipe.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Recipe.xlsx
@@ -615,12 +615,12 @@
       </c>
       <c r="B4" s="21" t="inlineStr">
         <is>
-          <t>채소죽 만들기</t>
+          <t>??? ???</t>
         </is>
       </c>
       <c r="C4" s="21" t="inlineStr">
         <is>
-          <t>쌀과 채소를 함께 넣고 오래 끓여 굶주린 이들에게 나눌 채소죽을 만든다.</t>
+          <t>?? ??? ?? ?? ?? ?? ??? ???? ?? ???? ???.</t>
         </is>
       </c>
       <c r="D4" s="21" t="inlineStr">
@@ -651,13 +651,39 @@
       <c r="O4" s="18" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="18" t="n"/>
-      <c r="B5" s="18" t="n"/>
-      <c r="C5" s="18" t="n"/>
-      <c r="D5" s="18" t="n"/>
-      <c r="E5" s="18" t="n"/>
-      <c r="F5" s="18" t="n"/>
-      <c r="G5" s="18" t="n"/>
+      <c r="A5" s="21" t="inlineStr">
+        <is>
+          <t>OO_Recipe_KimchiStew_1</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>김치찌개 조리법</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr">
+        <is>
+          <t>김치와 청양고추를 알맞은 조리도구에 올려 김치찌개를 완성합니다.</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>OO_KimchiStew_1</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>Ing_Kimch_01|Ing_ChiliPepper_01</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>가마솥|도마</t>
+        </is>
+      </c>
       <c r="H5" s="18" t="n"/>
       <c r="I5" s="18" t="n"/>
       <c r="J5" s="18" t="n"/>

--- a/JsonConverter/ExcelFiles/OO_Recipe.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Recipe.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,16 @@
       <b val="1"/>
     </font>
     <font/>
+    <font>
+      <name val="?? ??"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +60,11 @@
         <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -65,7 +78,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -75,6 +88,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -818,6 +837,122 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>OO_Recipe_KoreanCake_1</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>떡 만들기</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>쌀 1개를 절구에 넣어 떡 1개를 만듭니다.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>OO_KoreanCake_1</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Ing_Rice_01</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>절구</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Ing_Rice_01</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>Julgu</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>떡은 쌀 1개를 절구에 넣으면 바로 완성됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>OO_Recipe_HoneyKoreanCake_1</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>꿀떡 만들기</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>떡 1개와 꿀 1개를 합쳐 꿀떡 1개를 만듭니다.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>OO_HoneyKoreanCake_1</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>OO_KoreanCake_1|Ing_Honey_01</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>선택지 조합</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>OO_KoreanCake_1|Ing_Honey_01</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>1|1</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Choice</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>떡과 꿀이 각각 1개 이상 있으면 꿀떡을 만들 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/JsonConverter/ExcelFiles/OO_Recipe.xlsx
+++ b/JsonConverter/ExcelFiles/OO_Recipe.xlsx
@@ -38,7 +38,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +65,21 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -78,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -94,6 +109,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -460,204 +484,204 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="28" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="58" customWidth="1" min="12" max="12"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="33" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>레시피 ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>요리 이름</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>요리 방법 설명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>완성 음식 ID</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>기존 필요 재료 ID 목록(| 구분)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>기존 같은 재료 허용 횟수</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>기존 필요 조리 도구</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>필요 재료 ID 목록(| 구분)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>필요 재료 수량 목록(| 구분)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>필요 조리도구 ID 목록(| 구분)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>완성 수량</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>수량 부족 안내 문구</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>ResultItemId</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>RequiredIngredients</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>MaxDuplicateCount</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>RequiredTool</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>RequiredIngredientIds</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>RequiredIngredientCounts</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>RequiredToolIds</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>ResultCount</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>QuantityGuideText</t>
         </is>
@@ -950,6 +974,122 @@
       <c r="L8" s="5" t="inlineStr">
         <is>
           <t>떡과 꿀이 각각 1개 이상 있으면 꿀떡을 만들 수 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>OO_Recipe_CarrotStarch_1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>당근전분 만들기</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>당근 1개와 떡 1개를 레시피 조합 칸에 올려 당근전분을 만듭니다.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OO_CarrotStarch_1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Ing_Carrot_01|OO_KoreanCake_1</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>레시피 조합</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Ing_Carrot_01|OO_KoreanCake_1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1|1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>RecipeMix</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>당근전분은 당근 1개와 떡 1개가 필요합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>OO_Recipe_CarrotCake_1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>당근전 만들기</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>당근전분 1개를 가마솥에 넣어 당근전을 완성합니다.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OO_CarrotCake_1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>OO_CarrotStarch_1</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>가마솥</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OO_CarrotStarch_1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Cauldron</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>당근전은 당근전분 1개를 가마솥에 넣으면 완성됩니다.</t>
         </is>
       </c>
     </row>
